--- a/darts_data.xlsx
+++ b/darts_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livenorthumbriaac-my.sharepoint.com/personal/matthew_haigh_northumbria_ac_uk/Documents/Darts stats 26_27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="375" documentId="13_ncr:1_{A548E091-66FB-4CC8-9AF3-D8F9763DD490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF266137-3891-4515-B4FE-F8787B246896}"/>
+  <xr:revisionPtr revIDLastSave="467" documentId="13_ncr:1_{A548E091-66FB-4CC8-9AF3-D8F9763DD490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C994A8F8-8349-4D7D-ADEC-478A70506BF9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{671F733F-72D7-476C-A8D6-9E6C4068A91D}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="74">
   <si>
     <t>Venue</t>
   </si>
@@ -486,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -528,6 +528,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2413,27 +2416,66 @@
       <c r="C20" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="19"/>
+      <c r="D20" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0</v>
+      </c>
+      <c r="H20" s="17">
+        <v>0</v>
+      </c>
+      <c r="I20" s="17">
+        <v>0</v>
+      </c>
+      <c r="J20" s="18">
+        <v>0</v>
+      </c>
+      <c r="K20" s="19">
+        <v>0</v>
+      </c>
+      <c r="L20" s="42">
+        <v>0</v>
+      </c>
       <c r="O20" s="25"/>
+      <c r="P20" s="42">
+        <v>103</v>
+      </c>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="42"/>
+      <c r="T20" s="42"/>
+      <c r="U20" s="42"/>
+      <c r="V20" s="42"/>
+      <c r="W20" s="42"/>
+      <c r="X20" s="42"/>
+      <c r="Y20" s="43"/>
       <c r="Z20" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB20" s="30"/>
-      <c r="AC20" s="33"/>
+        <v>0.1</v>
+      </c>
+      <c r="AB20" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="33">
+        <v>0</v>
+      </c>
       <c r="AD20" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
@@ -2446,27 +2488,70 @@
       <c r="C21" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="19"/>
+      <c r="D21" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0</v>
+      </c>
+      <c r="F21" s="10">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>2</v>
+      </c>
+      <c r="H21" s="20">
+        <v>0</v>
+      </c>
+      <c r="I21" s="21">
+        <v>0</v>
+      </c>
+      <c r="J21" s="18">
+        <v>2</v>
+      </c>
+      <c r="K21" s="19">
+        <v>1</v>
+      </c>
+      <c r="L21" s="42">
+        <v>0</v>
+      </c>
       <c r="O21" s="25"/>
+      <c r="P21" s="42">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="42">
+        <v>100</v>
+      </c>
+      <c r="R21" s="42">
+        <v>123</v>
+      </c>
+      <c r="S21" s="42"/>
+      <c r="T21" s="42"/>
+      <c r="U21" s="42"/>
+      <c r="V21" s="42"/>
+      <c r="W21" s="42"/>
+      <c r="X21" s="42"/>
+      <c r="Y21" s="43"/>
       <c r="Z21" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA21" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB21" s="30"/>
-      <c r="AC21" s="33"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="AB21" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="33">
+        <v>0</v>
+      </c>
       <c r="AD21" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.3</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
@@ -2479,27 +2564,68 @@
       <c r="C22" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="19"/>
+      <c r="D22" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7">
+        <v>1</v>
+      </c>
+      <c r="G22" s="8">
+        <v>2</v>
+      </c>
+      <c r="H22" s="21">
+        <v>0</v>
+      </c>
+      <c r="I22" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="J22" s="18">
+        <v>2</v>
+      </c>
+      <c r="K22" s="19">
+        <v>1</v>
+      </c>
+      <c r="L22" s="42">
+        <v>70</v>
+      </c>
       <c r="O22" s="25"/>
+      <c r="P22" s="42">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="42">
+        <v>140</v>
+      </c>
+      <c r="R22" s="42"/>
+      <c r="S22" s="42"/>
+      <c r="T22" s="42"/>
+      <c r="U22" s="42"/>
+      <c r="V22" s="42"/>
+      <c r="W22" s="42"/>
+      <c r="X22" s="42"/>
+      <c r="Y22" s="43"/>
       <c r="Z22" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA22" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB22" s="30"/>
-      <c r="AC22" s="33"/>
+        <v>0.2</v>
+      </c>
+      <c r="AB22" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="33">
+        <v>0</v>
+      </c>
       <c r="AD22" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.7</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
@@ -2512,27 +2638,66 @@
       <c r="C23" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="19"/>
+      <c r="D23" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1</v>
+      </c>
+      <c r="F23" s="10">
+        <v>1</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="17">
+        <v>0.33</v>
+      </c>
+      <c r="I23" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="J23" s="18">
+        <v>0</v>
+      </c>
+      <c r="K23" s="19">
+        <v>0</v>
+      </c>
+      <c r="L23" s="42">
+        <v>0</v>
+      </c>
       <c r="O23" s="25"/>
+      <c r="P23" s="42">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="42"/>
+      <c r="R23" s="42"/>
+      <c r="S23" s="42"/>
+      <c r="T23" s="42"/>
+      <c r="U23" s="42"/>
+      <c r="V23" s="42"/>
+      <c r="W23" s="42"/>
+      <c r="X23" s="42"/>
+      <c r="Y23" s="43"/>
       <c r="Z23" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB23" s="30"/>
-      <c r="AC23" s="33"/>
+        <v>0.1</v>
+      </c>
+      <c r="AB23" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="33">
+        <v>0</v>
+      </c>
       <c r="AD23" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.93</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
@@ -2545,27 +2710,66 @@
       <c r="C24" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="19"/>
+      <c r="D24" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1</v>
+      </c>
+      <c r="F24" s="7">
+        <v>0</v>
+      </c>
+      <c r="G24" s="8">
+        <v>2</v>
+      </c>
+      <c r="H24" s="20">
+        <v>0.33</v>
+      </c>
+      <c r="I24" s="17">
+        <v>0</v>
+      </c>
+      <c r="J24" s="18">
+        <v>2</v>
+      </c>
+      <c r="K24" s="19">
+        <v>0</v>
+      </c>
+      <c r="L24" s="42">
+        <v>55</v>
+      </c>
       <c r="O24" s="25"/>
+      <c r="P24" s="42">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
+      <c r="S24" s="42"/>
+      <c r="T24" s="42"/>
+      <c r="U24" s="42"/>
+      <c r="V24" s="42"/>
+      <c r="W24" s="42"/>
+      <c r="X24" s="42"/>
+      <c r="Y24" s="43"/>
       <c r="Z24" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA24" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB24" s="30"/>
-      <c r="AC24" s="33"/>
+        <v>0.1</v>
+      </c>
+      <c r="AB24" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="33">
+        <v>0</v>
+      </c>
       <c r="AD24" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
@@ -2578,27 +2782,72 @@
       <c r="C25" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="19"/>
+      <c r="D25" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="10">
+        <v>1</v>
+      </c>
+      <c r="F25" s="10">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8">
+        <v>2</v>
+      </c>
+      <c r="H25" s="21">
+        <v>0.33</v>
+      </c>
+      <c r="I25" s="21">
+        <v>0</v>
+      </c>
+      <c r="J25" s="18">
+        <v>2</v>
+      </c>
+      <c r="K25" s="19">
+        <v>1</v>
+      </c>
+      <c r="L25" s="42">
+        <v>0</v>
+      </c>
       <c r="O25" s="25"/>
+      <c r="P25" s="42">
+        <v>100</v>
+      </c>
+      <c r="Q25" s="42">
+        <v>140</v>
+      </c>
+      <c r="R25" s="42">
+        <v>100</v>
+      </c>
+      <c r="S25" s="42">
+        <v>100</v>
+      </c>
+      <c r="T25" s="42"/>
+      <c r="U25" s="42"/>
+      <c r="V25" s="42"/>
+      <c r="W25" s="42"/>
+      <c r="X25" s="42"/>
+      <c r="Y25" s="43"/>
       <c r="Z25" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA25" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB25" s="30"/>
-      <c r="AC25" s="33"/>
-      <c r="AD25" s="19">
+        <v>0.4</v>
+      </c>
+      <c r="AB25" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="33">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="40">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.73</v>
+      </c>
+      <c r="AE25" s="40" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
@@ -2811,15 +3060,17 @@
       <c r="J32" s="18"/>
       <c r="K32" s="19"/>
       <c r="O32" s="25"/>
-      <c r="Z32" s="14">
+      <c r="Z32" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA32" s="14">
+      <c r="AA32" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD32" s="14">
+      <c r="AB32" s="19"/>
+      <c r="AC32" s="41"/>
+      <c r="AD32" s="19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2842,15 +3093,17 @@
       <c r="J33" s="18"/>
       <c r="K33" s="19"/>
       <c r="O33" s="25"/>
-      <c r="Z33" s="14">
+      <c r="Z33" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA33" s="14">
+      <c r="AA33" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD33" s="14">
+      <c r="AB33" s="19"/>
+      <c r="AC33" s="41"/>
+      <c r="AD33" s="19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2873,15 +3126,17 @@
       <c r="J34" s="18"/>
       <c r="K34" s="19"/>
       <c r="O34" s="25"/>
-      <c r="Z34" s="14">
+      <c r="Z34" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA34" s="14">
+      <c r="AA34" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD34" s="14">
+      <c r="AB34" s="19"/>
+      <c r="AC34" s="41"/>
+      <c r="AD34" s="19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2904,15 +3159,17 @@
       <c r="J35" s="18"/>
       <c r="K35" s="19"/>
       <c r="O35" s="25"/>
-      <c r="Z35" s="14">
+      <c r="Z35" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA35" s="14">
+      <c r="AA35" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD35" s="14">
+      <c r="AB35" s="19"/>
+      <c r="AC35" s="41"/>
+      <c r="AD35" s="19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2935,15 +3192,17 @@
       <c r="J36" s="18"/>
       <c r="K36" s="19"/>
       <c r="O36" s="25"/>
-      <c r="Z36" s="14">
+      <c r="Z36" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="14">
+      <c r="AA36" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD36" s="14">
+      <c r="AB36" s="19"/>
+      <c r="AC36" s="41"/>
+      <c r="AD36" s="19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2966,15 +3225,17 @@
       <c r="J37" s="18"/>
       <c r="K37" s="19"/>
       <c r="O37" s="25"/>
-      <c r="Z37" s="14">
+      <c r="Z37" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA37" s="14">
+      <c r="AA37" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD37" s="14">
+      <c r="AB37" s="19"/>
+      <c r="AC37" s="41"/>
+      <c r="AD37" s="19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7054,7 +7315,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>3</v>
       </c>
@@ -7071,7 +7332,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>3</v>
       </c>
@@ -7088,7 +7349,7 @@
         <v>1.6300000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>3</v>
       </c>
@@ -7105,7 +7366,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>3</v>
       </c>
@@ -7122,7 +7383,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>3</v>
       </c>
@@ -7139,7 +7400,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>28</v>
       </c>
@@ -7156,7 +7417,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>4</v>
       </c>
@@ -7166,8 +7427,17 @@
       <c r="C23" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23">
+        <v>3.73</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>4</v>
       </c>
@@ -7177,8 +7447,14 @@
       <c r="C24" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>4</v>
       </c>
@@ -7188,8 +7464,14 @@
       <c r="C25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4</v>
       </c>
@@ -7199,8 +7481,14 @@
       <c r="C26" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26">
+        <v>2.4300000000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>4</v>
       </c>
@@ -7210,8 +7498,14 @@
       <c r="C27" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>4</v>
       </c>
@@ -7221,8 +7515,14 @@
       <c r="C28" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>28</v>
       </c>
@@ -7239,7 +7539,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>5</v>
       </c>
@@ -7250,7 +7550,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>5</v>
       </c>
@@ -7261,7 +7561,7 @@
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>5</v>
       </c>
@@ -9151,8 +9451,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:E21">
-    <sortCondition descending="1" ref="E16:E21"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A23:E28">
+    <sortCondition descending="1" ref="E23:E28"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
